--- a/daily_matches/job_matches_2026-06-13.xlsx
+++ b/daily_matches/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, MLflow</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, AWS SageMaker, Data Lake, Kinesis, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7edd80e431e58210</t>
+          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, MLflow</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af97ac7780e4ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gen AI / Agentic AI Developer</t>
+          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, GCP Vertex AI</t>
+          <t>Data Scientist, RAG, S3, Athena, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25e0dd734111670</t>
+          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI / Agentic AI Developer</t>
+          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, GCP Vertex AI</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab260e8ebf0751</t>
+          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full-Stack &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeus Industrial Products</t>
+          <t>SS8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orangeburg, SC, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Cortex, CI/CD</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269e5c23a0f843a</t>
+          <t>https://www.indeed.com/viewjob?jk=85f6f808b20c69bf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer/Developer - Onsite</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b3de87b42f6fb87</t>
+          <t>https://www.indeed.com/viewjob?jk=d41f7e96a82028ca</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Technology Support Engineer/Analyst</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Databricks, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8a95dba210bad6</t>
+          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>QuidelOrtho Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Dataflow, CI/CD, GitHub Actions, Git, Power BI, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Databricks, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
+          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Semi Sr Data Analyst (Strategic Finance and Operations) – Data Analyst</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DISTILLERY</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ea557f4455c7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=44c1d58b67327ca1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bigstone Health Commission</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83684cbe530e29</t>
+          <t>https://www.indeed.com/viewjob?jk=aab6e44d46a0c0c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior AI Solutions Engineer – AI Taskforce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Tencate Grass</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb3976c5d11813</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8abcc8406e7f3a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Data Scientist, Audience Analytics for Healthy Communities</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Fors Marsh</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, Tableau, Power BI, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b52d14d72798735b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d42896a436d635</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer 3, Business Systems (CPQ)</t>
+          <t>Senior Data Scientist, Audience Analytics for Healthy Communities</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Fors Marsh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MongoDB, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, Tableau, Power BI, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0832fd5178908d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ee8cf7dda200d7c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Cain Watters &amp; Associates</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Python, SQL, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, RAG, Data Lake, PySpark, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a90a1aeef717331d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Clever Real Estate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43481cef9476c9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0db1c27506cffeee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Card Data &amp; Analytics team</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>East Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,112 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ad1bc41a22fdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=e940661ccd598409</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Senior</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Arizona State University</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4e4063b8bf029b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b555eed8bdeeb54</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22996b96c7558879</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-13.xlsx
+++ b/daily_matches/job_matches_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - AI/ML SME</t>
+          <t>Senior AI Platform Engineer - Frisco</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, AWS SageMaker, Data Lake, Kinesis, MLflow</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599be78bf8533a28</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce8afdf7b1be95a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE), Advanced</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, PostgreSQL, MySQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cbdae324f66576f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b88b1bbfe5c80a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Data Engineer - Data Platform &amp; Lakehouse SME</t>
+          <t>Engineer I - Software Development (Python / AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Athena, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Jenkins, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544d4f30509bbb06</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca1556014bc8b9e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Java/Kotlin, Microservices)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d77b44f4a3db0af</t>
+          <t>https://www.indeed.com/viewjob?jk=f52bab0c10779e1f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-Stack &amp; AI Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SS8</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85f6f808b20c69bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cbef7ce458bb15ce</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Sr Data Analyst - Digital Ecommerce (Math/Stats, A/B testing, ML)(Remote Or Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BizTech Fusion</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d41f7e96a82028ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b8825d36e53f5aeb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Databricks, Kafka, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b31d482e2d3c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=95dd92700283dd37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/ML Data Engineer (Databricks)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>QuidelOrtho Corporation</t>
+          <t>Rebel Hotel Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Databricks, Kafka, Python, R, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859e7ca77b35594f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7675ba3b9559cca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Optimization, A/B Testing</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c1d58b67327ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe592be7ad8d325</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>AI Agent Engineer, Client Facing New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Observe.AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Apache Airflow, Jenkins, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Copilot, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,322 +811,112 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab6e44d46a0c0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f05ceaa6cea55e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior AI Solutions Engineer – AI Taskforce</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tencate Grass</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Snowflake, Databricks, PySpark, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8abcc8406e7f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1f4a5314135b71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Audience Analytics for Healthy Communities</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fors Marsh</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Tableau, Power BI, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, Snowflake, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d42896a436d635</t>
+          <t>https://www.indeed.com/viewjob?jk=33e4a913eaa3f53e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Audience Analytics for Healthy Communities</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fors Marsh</t>
+          <t>Forge Global</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Tableau, Power BI, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, Snowflake, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ee8cf7dda200d7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cain Watters &amp; Associates</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, PySpark, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb96a8e880376758</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Clever Real Estate</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0db1c27506cffeee</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>East Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e940661ccd598409</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Senior</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e4063b8bf029b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Terraform, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b555eed8bdeeb54</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Terraform, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22996b96c7558879</t>
+          <t>https://www.indeed.com/viewjob?jk=7dc32ae5c82392ee</t>
         </is>
       </c>
     </row>
